--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131535587</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534812</v>
+        <v>131534497</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,31 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756259</v>
+        <v>756253</v>
       </c>
       <c r="R5" t="n">
-        <v>7209023</v>
+        <v>7209061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,17 +1070,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534497</v>
+        <v>131534812</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,30 +1106,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756253</v>
+        <v>756259</v>
       </c>
       <c r="R6" t="n">
-        <v>7209061</v>
+        <v>7209023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,13 +1176,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79282</v>
+        <v>79285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131535637</v>
+        <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755819</v>
+        <v>756236</v>
       </c>
       <c r="R14" t="n">
-        <v>7209183</v>
+        <v>7209034</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska typiskt kantiga hål i gran</t>
+          <t>både färska och äldre hack i gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131535915</v>
+        <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>756236</v>
+        <v>755819</v>
       </c>
       <c r="R15" t="n">
-        <v>7209034</v>
+        <v>7209183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>både färska och äldre hack i gran</t>
+          <t>färska typiskt kantiga hål i gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,31 +2296,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2328,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R17" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,17 +2365,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,30 +2401,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2437,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R18" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,13 +2471,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131535587</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131534497</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131534812</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79285</v>
+        <v>79286</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,30 +2296,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2327,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R17" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,13 +2366,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2390,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,31 +2406,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2433,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R18" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,17 +2475,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131535587</v>
+        <v>131534812</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,30 +896,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756066</v>
+        <v>756259</v>
       </c>
       <c r="R4" t="n">
-        <v>7208917</v>
+        <v>7209023</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,13 +966,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -990,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534497</v>
+        <v>131535778</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1006,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756253</v>
+        <v>756107</v>
       </c>
       <c r="R5" t="n">
-        <v>7209061</v>
+        <v>7208973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1076,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534812</v>
+        <v>131535587</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,31 +1116,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756259</v>
+        <v>756066</v>
       </c>
       <c r="R6" t="n">
-        <v>7209023</v>
+        <v>7208917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,17 +1185,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131535778</v>
+        <v>131534497</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,31 +1221,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756107</v>
+        <v>756253</v>
       </c>
       <c r="R7" t="n">
-        <v>7208973</v>
+        <v>7209061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,17 +1290,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534812</v>
+        <v>131535587</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,31 +896,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -928,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756259</v>
+        <v>756066</v>
       </c>
       <c r="R4" t="n">
-        <v>7209023</v>
+        <v>7208917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,17 +965,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131535778</v>
+        <v>131534497</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,31 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756107</v>
+        <v>756253</v>
       </c>
       <c r="R5" t="n">
-        <v>7208973</v>
+        <v>7209061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1070,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131535587</v>
+        <v>131534812</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,30 +1106,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756066</v>
+        <v>756259</v>
       </c>
       <c r="R6" t="n">
-        <v>7208917</v>
+        <v>7209023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,13 +1176,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131534497</v>
+        <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,30 +1216,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756253</v>
+        <v>756107</v>
       </c>
       <c r="R7" t="n">
-        <v>7209061</v>
+        <v>7208973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,13 +1286,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,30 +1651,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R11" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,13 +1721,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,31 +1761,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R12" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,17 +1830,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79286</v>
+        <v>79292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131535595</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>131535379</v>
       </c>
       <c r="B18" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,31 +2296,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2328,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R17" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,17 +2365,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,30 +2401,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2437,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R18" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,13 +2471,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,31 +1651,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R11" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,17 +1720,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,30 +1756,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1792,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R12" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,13 +1826,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131535587</v>
+        <v>131534497</v>
       </c>
       <c r="B4" t="n">
         <v>79260</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756066</v>
+        <v>756253</v>
       </c>
       <c r="R4" t="n">
-        <v>7208917</v>
+        <v>7209061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534497</v>
+        <v>131534812</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1001,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756253</v>
+        <v>756259</v>
       </c>
       <c r="R5" t="n">
-        <v>7209061</v>
+        <v>7209023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1071,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534812</v>
+        <v>131535778</v>
       </c>
       <c r="B6" t="n">
         <v>57898</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756259</v>
+        <v>756107</v>
       </c>
       <c r="R6" t="n">
-        <v>7209023</v>
+        <v>7208973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+          <t>typiska barksprätt på granstam</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131535778</v>
+        <v>131535587</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,31 +1221,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756107</v>
+        <v>756066</v>
       </c>
       <c r="R7" t="n">
-        <v>7208973</v>
+        <v>7208917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,17 +1290,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534497</v>
+        <v>131535587</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756253</v>
+        <v>756066</v>
       </c>
       <c r="R4" t="n">
-        <v>7209061</v>
+        <v>7208917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534812</v>
+        <v>131534497</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,31 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756259</v>
+        <v>756253</v>
       </c>
       <c r="R5" t="n">
-        <v>7209023</v>
+        <v>7209061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,17 +1070,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131535778</v>
+        <v>131534812</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756107</v>
+        <v>756259</v>
       </c>
       <c r="R6" t="n">
-        <v>7208973</v>
+        <v>7209023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>typiska barksprätt på granstam</t>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131535587</v>
+        <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,30 +1216,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756066</v>
+        <v>756107</v>
       </c>
       <c r="R7" t="n">
-        <v>7208917</v>
+        <v>7208973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,13 +1286,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,30 +2296,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2327,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R17" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,13 +2366,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2390,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,31 +2406,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2433,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R18" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,17 +2475,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131535587</v>
+        <v>131534497</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756066</v>
+        <v>756253</v>
       </c>
       <c r="R4" t="n">
-        <v>7208917</v>
+        <v>7209061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534497</v>
+        <v>131534812</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1001,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756253</v>
+        <v>756259</v>
       </c>
       <c r="R5" t="n">
-        <v>7209061</v>
+        <v>7209023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1071,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534812</v>
+        <v>131535778</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756259</v>
+        <v>756107</v>
       </c>
       <c r="R6" t="n">
-        <v>7209023</v>
+        <v>7208973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+          <t>typiska barksprätt på granstam</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131535778</v>
+        <v>131535587</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,31 +1221,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756107</v>
+        <v>756066</v>
       </c>
       <c r="R7" t="n">
-        <v>7208973</v>
+        <v>7208917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,17 +1290,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,30 +1651,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R11" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,13 +1721,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,31 +1761,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R12" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,17 +1830,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131535595</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>131535379</v>
       </c>
       <c r="B18" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534497</v>
+        <v>131535587</v>
       </c>
       <c r="B4" t="n">
         <v>79264</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756253</v>
+        <v>756066</v>
       </c>
       <c r="R4" t="n">
-        <v>7209061</v>
+        <v>7208917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534812</v>
+        <v>131534497</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,31 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756259</v>
+        <v>756253</v>
       </c>
       <c r="R5" t="n">
-        <v>7209023</v>
+        <v>7209061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,17 +1070,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,7 +1095,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131535778</v>
+        <v>131534812</v>
       </c>
       <c r="B6" t="n">
         <v>57902</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756107</v>
+        <v>756259</v>
       </c>
       <c r="R6" t="n">
-        <v>7208973</v>
+        <v>7209023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>typiska barksprätt på granstam</t>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131535587</v>
+        <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,30 +1216,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756066</v>
+        <v>756107</v>
       </c>
       <c r="R7" t="n">
-        <v>7208917</v>
+        <v>7208973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,13 +1286,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,31 +1651,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R11" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,17 +1720,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,30 +1756,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1792,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R12" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,13 +1826,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,31 +2296,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2328,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R17" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,17 +2365,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,30 +2401,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2437,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R18" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,13 +2471,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131535587</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>131534497</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131534812</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79296</v>
+        <v>79298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131535379</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>131535595</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,30 +1651,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R11" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,13 +1721,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,31 +1761,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R12" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,17 +1830,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,31 +1651,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R11" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,17 +1720,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,30 +1756,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1792,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R12" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,13 +1826,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131535587</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534497</v>
+        <v>131534812</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1001,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756253</v>
+        <v>756259</v>
       </c>
       <c r="R5" t="n">
-        <v>7209061</v>
+        <v>7209023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,13 +1071,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534812</v>
+        <v>131534497</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,31 +1111,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756259</v>
+        <v>756253</v>
       </c>
       <c r="R6" t="n">
-        <v>7209023</v>
+        <v>7209061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,17 +1180,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,31 +1651,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1683,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R11" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,17 +1720,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,30 +1756,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1792,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R12" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,13 +1826,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79298</v>
+        <v>79301</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B17" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,30 +2296,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2327,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R17" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,13 +2366,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2390,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,31 +2406,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2433,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R18" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,17 +2475,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131535587</v>
+        <v>131534812</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,30 +896,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756066</v>
+        <v>756259</v>
       </c>
       <c r="R4" t="n">
-        <v>7208917</v>
+        <v>7209023</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,13 +966,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -990,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534812</v>
+        <v>131535778</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756259</v>
+        <v>756107</v>
       </c>
       <c r="R5" t="n">
-        <v>7209023</v>
+        <v>7208973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1078,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+          <t>typiska barksprätt på granstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534497</v>
+        <v>131535587</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756253</v>
+        <v>756066</v>
       </c>
       <c r="R6" t="n">
-        <v>7209061</v>
+        <v>7208917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131535778</v>
+        <v>131534497</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,31 +1221,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756107</v>
+        <v>756253</v>
       </c>
       <c r="R7" t="n">
-        <v>7208973</v>
+        <v>7209061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,17 +1290,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>131534714</v>
       </c>
       <c r="B12" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79301</v>
+        <v>79306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131535595</v>
       </c>
       <c r="B17" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>131535379</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131535719</v>
+        <v>131534714</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,30 +1651,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755910</v>
+        <v>756237</v>
       </c>
       <c r="R11" t="n">
-        <v>7209115</v>
+        <v>7209026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,13 +1721,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131534714</v>
+        <v>131535719</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,31 +1761,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>756237</v>
+        <v>755910</v>
       </c>
       <c r="R12" t="n">
-        <v>7209026</v>
+        <v>7209115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,17 +1830,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B17" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,31 +2296,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2328,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R17" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,17 +2365,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2395,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,30 +2401,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2437,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R18" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,13 +2471,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131535664</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131535523</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534812</v>
+        <v>131535587</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,31 +896,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -928,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756259</v>
+        <v>756066</v>
       </c>
       <c r="R4" t="n">
-        <v>7209023</v>
+        <v>7208917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,17 +965,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131535778</v>
+        <v>131534497</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,31 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756107</v>
+        <v>756253</v>
       </c>
       <c r="R5" t="n">
-        <v>7208973</v>
+        <v>7209061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1070,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1105,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131535587</v>
+        <v>131534812</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,30 +1106,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756066</v>
+        <v>756259</v>
       </c>
       <c r="R6" t="n">
-        <v>7208917</v>
+        <v>7209023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,13 +1176,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131534497</v>
+        <v>131535778</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,30 +1216,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756253</v>
+        <v>756107</v>
       </c>
       <c r="R7" t="n">
-        <v>7209061</v>
+        <v>7208973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,13 +1286,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>131535361</v>
       </c>
       <c r="B8" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131534643</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>131534964</v>
       </c>
       <c r="B10" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>131534714</v>
       </c>
       <c r="B11" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>131535719</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>131535811</v>
       </c>
       <c r="B13" t="n">
-        <v>79306</v>
+        <v>79308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>131535915</v>
       </c>
       <c r="B14" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>131535637</v>
       </c>
       <c r="B15" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131535873</v>
       </c>
       <c r="B16" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535379</v>
+        <v>131535595</v>
       </c>
       <c r="B17" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,30 +2296,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2327,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>756199</v>
+        <v>755855</v>
       </c>
       <c r="R17" t="n">
-        <v>7208936</v>
+        <v>7209154</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,13 +2366,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2390,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535595</v>
+        <v>131535379</v>
       </c>
       <c r="B18" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,31 +2406,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2433,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755855</v>
+        <v>756199</v>
       </c>
       <c r="R18" t="n">
-        <v>7209154</v>
+        <v>7208936</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,17 +2475,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>131534594</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>131535794</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131535664</v>
+        <v>131535811</v>
       </c>
       <c r="B2" t="n">
-        <v>79276</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755782</v>
+        <v>756092</v>
       </c>
       <c r="R2" t="n">
-        <v>7209227</v>
+        <v>7208958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,14 +780,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131535523</v>
+        <v>131534497</v>
       </c>
       <c r="B3" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>756184</v>
+        <v>756253</v>
       </c>
       <c r="R3" t="n">
-        <v>7208947</v>
+        <v>7209061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,14 +885,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131535587</v>
+        <v>131534594</v>
       </c>
       <c r="B4" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756066</v>
+        <v>756247</v>
       </c>
       <c r="R4" t="n">
-        <v>7208917</v>
+        <v>7209053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,14 +990,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534497</v>
+        <v>131534643</v>
       </c>
       <c r="B5" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756253</v>
+        <v>756229</v>
       </c>
       <c r="R5" t="n">
-        <v>7209061</v>
+        <v>7209044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,42 +1095,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534812</v>
+        <v>131535379</v>
       </c>
       <c r="B6" t="n">
-        <v>57914</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756259</v>
+        <v>756199</v>
       </c>
       <c r="R6" t="n">
-        <v>7209023</v>
+        <v>7208936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,17 +1175,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>påbörjat bohål i granstam, art-typisk storlek</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,42 +1200,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131535778</v>
+        <v>131535521</v>
       </c>
       <c r="B7" t="n">
-        <v>57914</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1248,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756107</v>
+        <v>756141</v>
       </c>
       <c r="R7" t="n">
-        <v>7208973</v>
+        <v>7208910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,17 +1280,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,42 +1305,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131535361</v>
+        <v>131535523</v>
       </c>
       <c r="B8" t="n">
-        <v>57914</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1358,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>756201</v>
+        <v>756184</v>
       </c>
       <c r="R8" t="n">
-        <v>7208948</v>
+        <v>7208947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,17 +1385,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,14 +1410,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534643</v>
+        <v>131535587</v>
       </c>
       <c r="B9" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1467,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>756229</v>
+        <v>756066</v>
       </c>
       <c r="R9" t="n">
-        <v>7209044</v>
+        <v>7208917</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,42 +1515,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131534964</v>
+        <v>131535664</v>
       </c>
       <c r="B10" t="n">
-        <v>57914</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1573,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>756206</v>
+        <v>755782</v>
       </c>
       <c r="R10" t="n">
-        <v>7208978</v>
+        <v>7209227</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,17 +1595,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1643,11 +1623,11 @@
         <v>131535719</v>
       </c>
       <c r="B11" t="n">
-        <v>79276</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1745,42 +1725,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131534714</v>
+        <v>131535794</v>
       </c>
       <c r="B12" t="n">
-        <v>57914</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>756237</v>
+        <v>756108</v>
       </c>
       <c r="R12" t="n">
-        <v>7209026</v>
+        <v>7208959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,17 +1805,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på granstam</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1855,32 +1830,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131535811</v>
+        <v>131535873</v>
       </c>
       <c r="B13" t="n">
-        <v>79308</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>756092</v>
+        <v>756110</v>
       </c>
       <c r="R13" t="n">
-        <v>7208958</v>
+        <v>7208946</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,42 +1935,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131535915</v>
+        <v>131535946</v>
       </c>
       <c r="B14" t="n">
-        <v>57911</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2003,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>756236</v>
+        <v>756372</v>
       </c>
       <c r="R14" t="n">
-        <v>7209034</v>
+        <v>7209007</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,17 +2015,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>både färska och äldre hack i gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2070,42 +2040,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131535637</v>
+        <v>131535690</v>
       </c>
       <c r="B15" t="n">
-        <v>57911</v>
+        <v>79351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2113,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755819</v>
+        <v>755898</v>
       </c>
       <c r="R15" t="n">
-        <v>7209183</v>
+        <v>7209132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,17 +2120,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska typiskt kantiga hål i gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2180,41 +2145,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131535873</v>
+        <v>131535637</v>
       </c>
       <c r="B16" t="n">
-        <v>79276</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2222,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>756110</v>
+        <v>755819</v>
       </c>
       <c r="R16" t="n">
-        <v>7208946</v>
+        <v>7209183</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,13 +2226,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska typiskt kantiga hål i gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2285,41 +2255,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131535379</v>
+        <v>131535915</v>
       </c>
       <c r="B17" t="n">
-        <v>79276</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2327,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>756199</v>
+        <v>756236</v>
       </c>
       <c r="R17" t="n">
-        <v>7208936</v>
+        <v>7209034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,13 +2336,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>både färska och äldre hack i gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2390,10 +2365,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131535595</v>
+        <v>131534714</v>
       </c>
       <c r="B18" t="n">
-        <v>57914</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755855</v>
+        <v>756237</v>
       </c>
       <c r="R18" t="n">
-        <v>7209154</v>
+        <v>7209026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2500,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131535794</v>
+        <v>131534812</v>
       </c>
       <c r="B19" t="n">
-        <v>79276</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,30 +2486,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2542,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>756108</v>
+        <v>756259</v>
       </c>
       <c r="R19" t="n">
-        <v>7208959</v>
+        <v>7209023</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,13 +2556,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>påbörjat bohål i granstam, art-typisk storlek</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2605,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131534594</v>
+        <v>131534964</v>
       </c>
       <c r="B20" t="n">
-        <v>79276</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,30 +2596,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2647,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>756247</v>
+        <v>756206</v>
       </c>
       <c r="R20" t="n">
-        <v>7209053</v>
+        <v>7208978</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,13 +2666,17 @@
           <t>2026-03-06</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2707,6 +2692,662 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131535361</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Olofsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>756201</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7208948</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>barksprätt på granstam</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131535466</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Olofsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>756162</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7208896</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131535507</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Olofsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>756158</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7208909</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>barksprätt och bortfläkt bark på granstam</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131535595</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Olofsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>755855</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7209154</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131535778</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Olofsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>756107</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7208973</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131535958</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Olofsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>756374</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7209006</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på granstam</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33093-2025 artfynd.xlsx
+++ b/artfynd/A 33093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534594</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534643</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535379</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535521</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535523</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535587</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535664</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535719</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535794</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535873</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535946</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2142,6 +2212,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535690</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2252,6 +2327,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535637</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,6 +2442,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535915</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2472,6 +2557,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534714</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2582,6 +2672,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534812</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2692,6 +2787,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534964</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535361</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535466</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3022,6 +3132,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535507</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3132,6 +3247,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535595</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3242,6 +3362,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535778</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3348,8 +3473,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131535958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>